--- a/services_forms/004_facebook_likes_and_twitter_followers--services_forms.xlsx
+++ b/services_forms/004_facebook_likes_and_twitter_followers--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>order</t>
+          <t>order_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Order 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>order_note</t>
+          <t>order_note_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Order Note</t>
+          <t>Order Note 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>client_facebook_likes</t>
+          <t>client_facebook_likes_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Client Facebook Likes</t>
+          <t>Client Facebook Likes 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,7 +957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>client_twitter_followers</t>
+          <t>client_twitter_followers_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Order Note</t>
+          <t>Order Notes</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>order_note</t>
+          <t>order_note_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Order Note</t>
+          <t>Order Note 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>client_facebook_likes</t>
+          <t>client_facebook_likes_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Client Facebook Likes</t>
+          <t>Client Facebook Likes 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>client_twitter_followers</t>
+          <t>client_twitter_followers_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Client Twitter Followers</t>
+          <t>Client Twitter Followers 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
